--- a/expense_dashboard/templates/pivot_template.xlsx
+++ b/expense_dashboard/templates/pivot_template.xlsx
@@ -8,18 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\資誠claude code專案資料夾\invoice_excel_mapping\expense_dashboard\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA27FA5D-FB50-4CDD-A2AC-6F2EE14C3ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9F9F94D-C939-4785-B8C2-7C59CDEE48B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15465" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{59A39972-19DC-4FAC-9FF0-DBB75C953DFC}"/>
+    <workbookView xWindow="15465" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{2573DD42-5528-4BE5-8CB9-540C2F60DDE8}"/>
   </bookViews>
   <sheets>
-    <sheet name="儀表板" sheetId="1" r:id="rId1"/>
-    <sheet name="樞紐_供應商月份" sheetId="3" r:id="rId2"/>
-    <sheet name="樞紐_費用大類" sheetId="4" r:id="rId3"/>
-    <sheet name="樞紐_集團公司" sheetId="5" r:id="rId4"/>
-    <sheet name="樞紐_航線" sheetId="6" r:id="rId5"/>
-    <sheet name="明細" sheetId="2" r:id="rId6"/>
-    <sheet name="讀取失敗" sheetId="7" r:id="rId7"/>
+    <sheet name="儀表板_總覽" sheetId="1" r:id="rId1"/>
+    <sheet name="儀表板_運量航線" sheetId="2" r:id="rId2"/>
+    <sheet name="樞紐_每月費用大類" sheetId="4" r:id="rId3"/>
+    <sheet name="樞紐_年度比較" sheetId="5" r:id="rId4"/>
+    <sheet name="樞紐_供應商排名" sheetId="6" r:id="rId5"/>
+    <sheet name="樞紐_供應商月份" sheetId="7" r:id="rId6"/>
+    <sheet name="樞紐_費用大類" sheetId="8" r:id="rId7"/>
+    <sheet name="樞紐_集團公司" sheetId="9" r:id="rId8"/>
+    <sheet name="樞紐_運量" sheetId="10" r:id="rId9"/>
+    <sheet name="樞紐_單位成本_供應商" sheetId="11" r:id="rId10"/>
+    <sheet name="樞紐_單位成本_航線" sheetId="12" r:id="rId11"/>
+    <sheet name="樞紐_航線" sheetId="13" r:id="rId12"/>
+    <sheet name="明細" sheetId="3" r:id="rId13"/>
+    <sheet name="讀取失敗" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_SUPPLIER_供應商名稱">#N/A</definedName>
@@ -29,15 +36,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId8"/>
+    <pivotCache cacheId="24" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId9"/>
-        <x14:slicerCache r:id="rId10"/>
-        <x14:slicerCache r:id="rId11"/>
-        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId16"/>
+        <x14:slicerCache r:id="rId17"/>
+        <x14:slicerCache r:id="rId18"/>
+        <x14:slicerCache r:id="rId19"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -65,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="78">
   <si>
     <t>INVOICE DATE 發票日期</t>
   </si>
@@ -157,6 +164,39 @@
     <t>航線</t>
   </si>
   <si>
+    <t>運送型態</t>
+  </si>
+  <si>
+    <t>20GP 櫃數</t>
+  </si>
+  <si>
+    <t>40GP 櫃數</t>
+  </si>
+  <si>
+    <t>40HC 櫃數</t>
+  </si>
+  <si>
+    <t>45HC 櫃數</t>
+  </si>
+  <si>
+    <t>TEU</t>
+  </si>
+  <si>
+    <t>CBM</t>
+  </si>
+  <si>
+    <t>重量 KG</t>
+  </si>
+  <si>
+    <t>FCL 費用 (USD)</t>
+  </si>
+  <si>
+    <t>LCL 費用 (USD)</t>
+  </si>
+  <si>
+    <t>發票張數</t>
+  </si>
+  <si>
     <t>來源資料夾</t>
   </si>
   <si>
@@ -172,7 +212,25 @@
     <t>2026-01</t>
   </si>
   <si>
-    <t>各供應商每月費用 (USD)</t>
+    <t>USD 金額</t>
+  </si>
+  <si>
+    <t>發票數</t>
+  </si>
+  <si>
+    <t>TEU 數</t>
+  </si>
+  <si>
+    <t>CBM 數</t>
+  </si>
+  <si>
+    <t>每 TEU 成本 (USD)</t>
+  </si>
+  <si>
+    <t>每 CBM 成本 (USD)</t>
+  </si>
+  <si>
+    <t>每月 × 費用大類 (USD)</t>
   </si>
   <si>
     <t>列標籤</t>
@@ -184,13 +242,49 @@
     <t>欄標籤</t>
   </si>
   <si>
-    <t>USD 金額</t>
+    <t>今年 vs 去年：各月費用 (USD)</t>
+  </si>
+  <si>
+    <t>供應商費用排名與占比 (USD)</t>
+  </si>
+  <si>
+    <t>占總費用 %</t>
+  </si>
+  <si>
+    <t>各供應商每月費用 (USD)</t>
   </si>
   <si>
     <t>費用大類 × 供應商 (USD)</t>
   </si>
   <si>
     <t>集團公司 × 費用大類 (USD)</t>
+  </si>
+  <si>
+    <t>每月櫃型櫃數 (同一供應商的同一批貨只算一次)</t>
+  </si>
+  <si>
+    <t>20GP</t>
+  </si>
+  <si>
+    <t>40GP</t>
+  </si>
+  <si>
+    <t>40HC</t>
+  </si>
+  <si>
+    <t>45HC</t>
+  </si>
+  <si>
+    <t>單位成本 (供應商)：每 TEU = FCL 費用 / TEU，每 CBM = LCL 費用 / CBM</t>
+  </si>
+  <si>
+    <t>FCL 費用</t>
+  </si>
+  <si>
+    <t>LCL 費用</t>
+  </si>
+  <si>
+    <t>單位成本 (航線，TEU 前 20 名)</t>
   </si>
   <si>
     <t>航線費用前 20 名 (USD)</t>
@@ -205,19 +299,24 @@
     <t>-</t>
   </si>
   <si>
-    <t>物流費用分析儀表板 (金額：USD)</t>
+    <t>物流費用分析儀表板：總覽 (金額：USD)</t>
   </si>
   <si>
-    <t>點選上方篩選器可同時篩選全部圖表與樞紐分析表。資料在「明細」頁；樞紐分析表在「樞紐_」各頁。</t>
+    <t>點選篩選器可同時篩選兩頁儀表板的全部圖表與樞紐分析表。資料在「明細」頁；樞紐分析表在「樞紐_」各頁。</t>
+  </si>
+  <si>
+    <t>物流費用分析儀表板：運量與航線 (金額：USD)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="mmm\-dd\-yyyy"/>
     <numFmt numFmtId="177" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="178" formatCode="#,##0.000"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -276,7 +375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -292,20 +391,29 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -314,7 +422,37 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -359,6 +497,785 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot_template.xlsx]樞紐_每月費用大類!PT_每月費用大類</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>每月 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>× </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>費用大類 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>(USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_每月費用大類!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>(請按「啟用編輯」更新資料)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_每月費用大類!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_每月費用大類!$B$5:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A628-4260-B7DC-9BA4B2BA9E1D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="449671504"/>
+        <c:axId val="449672464"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="449671504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="449672464"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="449672464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="449671504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot_template.xlsx]樞紐_年度比較!PT_年度比較</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>今年 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>vs </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>去年：各月費用 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>(USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_年度比較!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_年度比較!$A$5:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_年度比較!$B$5:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FD59-4D3C-83FD-40873E6743F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="449667664"/>
+        <c:axId val="449671024"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="449667664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="449671024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="449671024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="449667664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -556,7 +1473,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-819B-4DB5-B692-7A1F1EEF3D2E}"/>
+              <c16:uniqueId val="{00000001-16D9-4472-8C6C-DAA4FF5C3977}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -570,11 +1487,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="761179471"/>
-        <c:axId val="761180911"/>
+        <c:axId val="449671984"/>
+        <c:axId val="449672944"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="761179471"/>
+        <c:axId val="449671984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -617,7 +1534,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761180911"/>
+        <c:crossAx val="449672944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -625,7 +1542,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="761180911"/>
+        <c:axId val="449672944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -676,7 +1593,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761179471"/>
+        <c:crossAx val="449671984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -746,7 +1663,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -945,7 +1862,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EF00-43AD-BC54-8BC1898F75DC}"/>
+              <c16:uniqueId val="{00000001-52BF-4946-8934-AF0DC5CEFBEE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -959,11 +1876,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="761181871"/>
-        <c:axId val="761181391"/>
+        <c:axId val="449669104"/>
+        <c:axId val="449673904"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="761181871"/>
+        <c:axId val="449669104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1006,7 +1923,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761181391"/>
+        <c:crossAx val="449673904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1014,7 +1931,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="761181391"/>
+        <c:axId val="449673904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1065,7 +1982,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761181871"/>
+        <c:crossAx val="449669104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1135,7 +2052,1099 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot_template.xlsx]樞紐_運量!PT_運量</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>每月櫃型櫃數</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_運量!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20GP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_運量!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_運量!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0506-4FCE-8E87-E08476429540}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_運量!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>40GP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_運量!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_運量!$C$4:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0506-4FCE-8E87-E08476429540}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_運量!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>40HC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_運量!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_運量!$D$4:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0506-4FCE-8E87-E08476429540}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_運量!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>45HC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_運量!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_運量!$E$4:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0506-4FCE-8E87-E08476429540}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="451308528"/>
+        <c:axId val="451304688"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="451308528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451304688"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="451304688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451308528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot_template.xlsx]樞紐_航線!PT_航線</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>航線費用前 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>20 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US"/>
+              <a:t>名 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>(USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>樞紐_航線!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>樞紐_航線!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>(請按「啟用編輯」更新資料)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>樞紐_航線!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4126-483E-8ABA-9878AEA140FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="451302768"/>
+        <c:axId val="451306128"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="451302768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451306128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="451306128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451302768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -1334,7 +3343,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EE45-4AA7-9BB5-6F55C7F80076}"/>
+              <c16:uniqueId val="{00000001-35CF-4DF1-9C43-DCB9D8913420}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1348,11 +3357,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="760709759"/>
-        <c:axId val="760710719"/>
+        <c:axId val="451304208"/>
+        <c:axId val="451307088"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="760709759"/>
+        <c:axId val="451304208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1395,7 +3404,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="760710719"/>
+        <c:crossAx val="451307088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1403,7 +3412,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="760710719"/>
+        <c:axId val="451307088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1454,395 +3463,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="760709759"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-TW"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-TW"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[pivot_template.xlsx]樞紐_航線!PT_航線</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="zh-TW" altLang="en-US"/>
-              <a:t>航線費用前 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW"/>
-              <a:t>20 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="zh-TW" altLang="en-US"/>
-              <a:t>名 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW"/>
-              <a:t>(USD)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-TW"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="zh-TW"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>樞紐_航線!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>合計</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>樞紐_航線!$A$4:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>(請按「啟用編輯」更新資料)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>樞紐_航線!$B$4:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-091F-46CC-A93A-9EF3D7D82AB5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="836307487"/>
-        <c:axId val="836307967"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="836307487"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-TW"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="836307967"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="836307967"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-TW"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="836307487"/>
+        <c:crossAx val="451304208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2072,6 +3693,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -2578,7 +4319,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2686,6 +4427,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2696,6 +4442,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2727,6 +4478,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2782,23 +4536,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2903,8 +4656,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3036,20 +4789,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3588,7 +5340,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -4092,7 +5844,1983 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>190497</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="國家">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F05E6B7-4F6C-D798-11D0-A550272068E5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="國家"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6597650" y="2292350"/>
+              <a:ext cx="1828800" cy="2336797"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100"/>
+                <a:t>此圖案代表交叉分析篩選器。Excel 2010 或更新版本支援交叉分析篩選器。
+如果圖案是在舊版 Excel 中修改，或如果活頁簿是在 Excel 2003 或較舊版本中儲存，則交叉分析篩選器無法使用。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>190497</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="SUPPLIER 供應商名稱">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF1249-1F28-158C-71F1-3D808C903872}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="SUPPLIER 供應商名稱"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6597650" y="2292350"/>
+              <a:ext cx="1828800" cy="2336797"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100"/>
+                <a:t>此圖案代表交叉分析篩選器。Excel 2010 或更新版本支援交叉分析篩選器。
+如果圖案是在舊版 Excel 中修改，或如果活頁簿是在 Excel 2003 或較舊版本中儲存，則交叉分析篩選器無法使用。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>190497</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="年">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5BEF47-50A2-0145-B1B9-12026E161CC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="年"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6597650" y="2292350"/>
+              <a:ext cx="1828800" cy="2336797"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100"/>
+                <a:t>此圖案代表交叉分析篩選器。Excel 2010 或更新版本支援交叉分析篩選器。
+如果圖案是在舊版 Excel 中修改，或如果活頁簿是在 Excel 2003 或較舊版本中儲存，則交叉分析篩選器無法使用。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>190497</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="費用大類">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FABA66A-E3DD-8254-7E91-7C1F49DA0AF3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="費用大類"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6597650" y="2292350"/>
+              <a:ext cx="1828800" cy="2336797"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100"/>
+                <a:t>此圖案代表交叉分析篩選器。Excel 2010 或更新版本支援交叉分析篩選器。
+如果圖案是在舊版 Excel 中修改，或如果活頁簿是在 Excel 2003 或較舊版本中儲存，則交叉分析篩選器無法使用。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>206375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="圖表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1800119B-3544-96BC-3787-3CB88ED7F960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>206375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="圖表 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF58B2E-F345-9860-7B62-E86C8BB41DB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="圖表 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{392793D5-4B66-8115-E111-C17CBBE67BF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="圖表 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA60F51-3035-B823-98BC-B39CE8D58A21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4111,10 +7839,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="國家">
+            <xdr:cNvPr id="2" name="國家 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C142EF-6B81-5BAB-730F-2351D6146BBA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03B46CDE-A4A5-247D-6411-D8387B7D5D85}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4126,7 +7854,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="國家"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="國家 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -4189,10 +7917,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="SUPPLIER 供應商名稱">
+            <xdr:cNvPr id="3" name="SUPPLIER 供應商名稱 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1989F041-1DAC-42DA-2113-893A7F190683}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8320BE77-99F4-B19A-E887-89F5A021FAD9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4204,7 +7932,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="SUPPLIER 供應商名稱"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="SUPPLIER 供應商名稱 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -4267,10 +7995,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="年">
+            <xdr:cNvPr id="4" name="年 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8025386E-2403-84B8-7F32-B807A74B2CA1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB6895C0-FE06-A2AC-56C4-62B791C9E935}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4282,7 +8010,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="年"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="年 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -4345,10 +8073,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="費用大類">
+            <xdr:cNvPr id="5" name="費用大類 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C889D99C-E850-646E-6585-07EE91A9F79D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2E75C2-19FB-364A-DEF7-B04213492AF1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4360,7 +8088,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="費用大類"/>
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="費用大類 1"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -4410,21 +8138,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>136525</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="6" name="圖表 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A37023FD-B2BF-2E6C-F13B-DBF8AF39A31E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C686782D-D613-6326-BC7D-0DD65ECD041D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4446,21 +8174,21 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>136525</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="7" name="圖表 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B177BF07-3802-5364-5DF9-01BCF4083C66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B61F53FA-1335-2852-4BD5-43B8D9CB6815}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4482,21 +8210,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="8" name="圖表 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC241A8-03FB-A959-9445-22CDF8E23902}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922764A3-0828-E8A8-4207-1A675C8FFD63}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4514,51 +8242,15 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="圖表 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265103F9-2FB8-A0D7-55B7-504A232CC848}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="" refreshedDate="46322.691716203706" missingItemsLimit="0" createdVersion="5" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{7AF95EEC-F09B-417E-B64E-6B48F4F004E3}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="" refreshedDate="46322.714291782409" missingItemsLimit="0" createdVersion="5" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{2116379A-D551-4788-BFB1-F68BB7109533}">
   <cacheSource type="worksheet">
     <worksheetSource name="明細表"/>
   </cacheSource>
-  <cacheFields count="32">
+  <cacheFields count="45">
     <cacheField name="INVOICE DATE 發票日期" numFmtId="176">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-01-02T00:00:00"/>
     </cacheField>
@@ -4656,12 +8348,47 @@
       </sharedItems>
     </cacheField>
     <cacheField name="年月" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="2026-01"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="航線" numFmtId="0">
       <sharedItems count="1">
         <s v="(請按「啟用編輯」更新資料)"/>
       </sharedItems>
+    </cacheField>
+    <cacheField name="運送型態" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="20GP 櫃數" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="40GP 櫃數" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="40HC 櫃數" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="45HC 櫃數" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="TEU" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="CBM" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="重量 KG" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="FCL 費用 (USD)" numFmtId="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="LCL 費用 (USD)" numFmtId="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="發票張數" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="來源資料夾" numFmtId="0">
       <sharedItems/>
@@ -4669,19 +8396,790 @@
     <cacheField name="來源檔案" numFmtId="0">
       <sharedItems/>
     </cacheField>
+    <cacheField name="每TEU成本" numFmtId="0" formula="'FCL 費用 (USD)'/TEU" databaseField="0"/>
+    <cacheField name="每CBM成本" numFmtId="0" formula="'LCL 費用 (USD)'/CBM" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1304380285"/>
+      <x14:pivotCacheDefinition pivotCacheId="341430193"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66F34C7E-7A27-426C-AF04-EB83D1BC8A0F}" name="PT_供應商月份" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59441AF4-8125-40B3-AB76-EFEC9D6613C4}" name="PT_KPI" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="發票數" fld="40" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DAA4AFA-A314-4EB1-B87A-1A30B3AC445C}" name="PT_單位成本_航線" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="29"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="FCL 費用" fld="38" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="LCL 費用" fld="39" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="29" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="20" filterVal="20"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70DDBC77-36D9-4F62-BB0B-F2342A2C38CB}" name="PT_航線" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="29"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="29" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="20" filterVal="20"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74879E4B-480A-4C12-8C3E-7BAC3D533B66}" name="PT_每月費用大類" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="28"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="22"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="22" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EF9368FE-44FB-4A88-B132-5308202E4733}" name="PT_年度比較" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="27"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="25"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="25" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF1B6232-FF2D-4EE7-BD7D-E8805FFE5E60}" name="PT_供應商排名" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="占總費用 %" fld="20" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="179"/>
+    <dataField name="發票數" fld="40" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8520181-2AA9-49B3-8BE3-010C13E278EF}" name="PT_供應商月份" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="45">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -4738,7 +9236,20 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="25"/>
@@ -4795,10 +9306,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD3D3D61-15A2-4C07-88B1-5DF496BBC14F}" name="PT_費用大類" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{79CE60CB-B5CC-47AF-ACA9-21415ABBEEC9}" name="PT_費用大類" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="45">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -4859,7 +9370,20 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="22"/>
@@ -4912,10 +9436,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D9EFF3F-05EA-4DBA-9036-4C610B59A5A4}" name="PT_集團公司" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B92C70EA-5B5A-4B5B-8511-52393FE7A533}" name="PT_集團公司" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="45">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -4981,7 +9505,20 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="3"/>
@@ -5034,10 +9571,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17648AE9-2A2C-4C3F-ACD9-B57B9B43E5E8}" name="PT_航線" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37530A12-3C84-4342-8793-715D8BF9AA36}" name="PT_運量" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:E5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="45">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -5063,7 +9600,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="177" showAll="0"/>
-    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
     <pivotField numFmtId="4" showAll="0"/>
     <pivotField showAll="0">
       <items count="2">
@@ -5086,8 +9623,120 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="28"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="20GP" fld="31" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="40GP" fld="32" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="40HC" fld="33" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="45HC" fld="34" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09538EE3-167C-43D0-B6EF-83A93C85EE91}" name="PT_單位成本_供應商" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="45">
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="2">
         <item x="0"/>
         <item t="default"/>
@@ -5104,9 +9753,64 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="29"/>
+    <field x="2"/>
   </rowFields>
   <rowItems count="2">
     <i>
@@ -5116,33 +9820,38 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
+  <dataFields count="6">
+    <dataField name="FCL 費用" fld="38" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="LCL 費用" fld="39" baseField="0" baseItem="0" numFmtId="4"/>
+    <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
+    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="29" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="20" filterVal="20"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -5155,15 +9864,22 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_國家" xr10:uid="{893B5034-CB27-45EF-8A5D-9A4464D36D85}" sourceName="國家">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_國家" xr10:uid="{0C6924CD-8AA9-4635-9554-748C1AFD8971}" sourceName="國家">
   <pivotTables>
-    <pivotTable tabId="3" name="PT_供應商月份"/>
-    <pivotTable tabId="4" name="PT_費用大類"/>
-    <pivotTable tabId="5" name="PT_集團公司"/>
-    <pivotTable tabId="6" name="PT_航線"/>
+    <pivotTable tabId="1" name="PT_KPI"/>
+    <pivotTable tabId="4" name="PT_每月費用大類"/>
+    <pivotTable tabId="5" name="PT_年度比較"/>
+    <pivotTable tabId="6" name="PT_供應商排名"/>
+    <pivotTable tabId="7" name="PT_供應商月份"/>
+    <pivotTable tabId="8" name="PT_費用大類"/>
+    <pivotTable tabId="9" name="PT_集團公司"/>
+    <pivotTable tabId="10" name="PT_運量"/>
+    <pivotTable tabId="11" name="PT_單位成本_供應商"/>
+    <pivotTable tabId="12" name="PT_單位成本_航線"/>
+    <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1304380285">
+    <tabular pivotCacheId="341430193">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -5173,15 +9889,22 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_SUPPLIER_供應商名稱" xr10:uid="{204FFC2D-FE27-4402-B2FB-EA7193ABA88C}" sourceName="SUPPLIER 供應商名稱">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_SUPPLIER_供應商名稱" xr10:uid="{FF7C1E86-ABD8-40ED-927B-F83DD9827A05}" sourceName="SUPPLIER 供應商名稱">
   <pivotTables>
-    <pivotTable tabId="3" name="PT_供應商月份"/>
-    <pivotTable tabId="4" name="PT_費用大類"/>
-    <pivotTable tabId="5" name="PT_集團公司"/>
-    <pivotTable tabId="6" name="PT_航線"/>
+    <pivotTable tabId="1" name="PT_KPI"/>
+    <pivotTable tabId="4" name="PT_每月費用大類"/>
+    <pivotTable tabId="5" name="PT_年度比較"/>
+    <pivotTable tabId="6" name="PT_供應商排名"/>
+    <pivotTable tabId="7" name="PT_供應商月份"/>
+    <pivotTable tabId="8" name="PT_費用大類"/>
+    <pivotTable tabId="9" name="PT_集團公司"/>
+    <pivotTable tabId="10" name="PT_運量"/>
+    <pivotTable tabId="11" name="PT_單位成本_供應商"/>
+    <pivotTable tabId="12" name="PT_單位成本_航線"/>
+    <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1304380285">
+    <tabular pivotCacheId="341430193">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -5191,15 +9914,22 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_年" xr10:uid="{8BE2EBCC-1ED9-4996-A0CE-DFD5504C56BD}" sourceName="年">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_年" xr10:uid="{F2556E91-E61A-4BB2-BC63-CDBBF5385AFB}" sourceName="年">
   <pivotTables>
-    <pivotTable tabId="3" name="PT_供應商月份"/>
-    <pivotTable tabId="4" name="PT_費用大類"/>
-    <pivotTable tabId="5" name="PT_集團公司"/>
-    <pivotTable tabId="6" name="PT_航線"/>
+    <pivotTable tabId="1" name="PT_KPI"/>
+    <pivotTable tabId="4" name="PT_每月費用大類"/>
+    <pivotTable tabId="5" name="PT_年度比較"/>
+    <pivotTable tabId="6" name="PT_供應商排名"/>
+    <pivotTable tabId="7" name="PT_供應商月份"/>
+    <pivotTable tabId="8" name="PT_費用大類"/>
+    <pivotTable tabId="9" name="PT_集團公司"/>
+    <pivotTable tabId="10" name="PT_運量"/>
+    <pivotTable tabId="11" name="PT_單位成本_供應商"/>
+    <pivotTable tabId="12" name="PT_單位成本_航線"/>
+    <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1304380285">
+    <tabular pivotCacheId="341430193">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -5209,15 +9939,22 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_費用大類" xr10:uid="{F98DE746-C07A-4E1C-AC3A-3534806F0181}" sourceName="費用大類">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_費用大類" xr10:uid="{D590E2D3-9E31-4AA7-88B3-D9194AC10CF4}" sourceName="費用大類">
   <pivotTables>
-    <pivotTable tabId="3" name="PT_供應商月份"/>
-    <pivotTable tabId="4" name="PT_費用大類"/>
-    <pivotTable tabId="5" name="PT_集團公司"/>
-    <pivotTable tabId="6" name="PT_航線"/>
+    <pivotTable tabId="1" name="PT_KPI"/>
+    <pivotTable tabId="4" name="PT_每月費用大類"/>
+    <pivotTable tabId="5" name="PT_年度比較"/>
+    <pivotTable tabId="6" name="PT_供應商排名"/>
+    <pivotTable tabId="7" name="PT_供應商月份"/>
+    <pivotTable tabId="8" name="PT_費用大類"/>
+    <pivotTable tabId="9" name="PT_集團公司"/>
+    <pivotTable tabId="10" name="PT_運量"/>
+    <pivotTable tabId="11" name="PT_單位成本_供應商"/>
+    <pivotTable tabId="12" name="PT_單位成本_航線"/>
+    <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1304380285">
+    <tabular pivotCacheId="341430193">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -5228,60 +9965,80 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="國家" xr10:uid="{9915313F-43B1-4468-978A-45E99F47DDF3}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
-  <slicer name="SUPPLIER 供應商名稱" xr10:uid="{22CA4A18-E665-4D49-81AD-987A6FF7CAC4}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
-  <slicer name="年" xr10:uid="{1AEB303C-9BEA-495A-9E43-563C99B71BA1}" cache="Slicer_年" caption="年" rowHeight="220133"/>
-  <slicer name="費用大類" xr10:uid="{5A27055F-CC97-4067-8AF5-860D9CF265FE}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
+  <slicer name="國家" xr10:uid="{6C0A8404-C2F8-42F6-A0D8-D97631E7AF5C}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
+  <slicer name="SUPPLIER 供應商名稱" xr10:uid="{3EC8ABB1-421E-4EBD-B770-4E091E13B5A6}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
+  <slicer name="年" xr10:uid="{9F12D052-DC10-416E-953D-CDD16B831657}" cache="Slicer_年" caption="年" rowHeight="220133"/>
+  <slicer name="費用大類" xr10:uid="{1804D4D9-A5A9-48CD-A28B-A817A42D98D7}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="國家 1" xr10:uid="{969B2AB5-429F-42A9-9902-307CD038B2DC}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
+  <slicer name="SUPPLIER 供應商名稱 1" xr10:uid="{AE1CD86A-2D57-4342-AD0D-552FB14B054D}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
+  <slicer name="年 1" xr10:uid="{1BCAE515-77E1-46CA-8EB2-722A022384D4}" cache="Slicer_年" caption="年" rowHeight="220133"/>
+  <slicer name="費用大類 1" xr10:uid="{4C065B2C-0853-40D9-944D-EB8FB1A19CA8}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{596A018C-DB9F-4A4C-B6CA-2F52F08B5802}" name="明細表" displayName="明細表" ref="A1:AF2" totalsRowShown="0">
-  <autoFilter ref="A1:AF2" xr:uid="{596A018C-DB9F-4A4C-B6CA-2F52F08B5802}"/>
-  <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{803D112B-5572-487D-9F1E-860E4854F818}" name="INVOICE DATE 發票日期" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{F359087A-713C-4C74-A174-C99488F4B360}" name="INVOICE NO 發票號碼"/>
-    <tableColumn id="3" xr3:uid="{A388FEBC-AF5B-4A0B-8884-890A9E024219}" name="SUPPLIER 供應商名稱"/>
-    <tableColumn id="4" xr3:uid="{8937CA7A-AF9F-4EA3-A8A2-5FDA9B4A2F5B}" name="CONSIGNEE 集團公司名稱"/>
-    <tableColumn id="5" xr3:uid="{E3575A06-8136-4BCC-BEC2-EEDA1B317AA7}" name="Description 費用名稱"/>
-    <tableColumn id="6" xr3:uid="{040A33BE-C9E7-42A0-BB39-3F2134C4387B}" name="AMOUNT 金額" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{194F4BD1-5423-4531-ACFC-13F8C0DB2A59}" name="VAT 稅額" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B9D372D7-6584-498B-938F-547FCBAED760}" name="Order No."/>
-    <tableColumn id="9" xr3:uid="{5CFCB6C7-4792-455D-8D92-194D2D5C53D7}" name="Arrive Date 到達日" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{4497388B-AA4D-4A29-830F-B09D7BC09756}" name="on board date 開船日" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{5C73AC33-DBA4-4505-BC12-CF87FA765EC6}" name="B/L NO. 提單號碼"/>
-    <tableColumn id="12" xr3:uid="{50152FA7-1A7B-4849-B48C-EA3B81339DF8}" name="MBL NO. 主提單號碼"/>
-    <tableColumn id="13" xr3:uid="{ECD4855F-4A9B-4629-B567-3F73B04C3CA5}" name="Port of Loading 啟運港"/>
-    <tableColumn id="14" xr3:uid="{4980CD19-44B5-40CD-BB1F-F51A98DCFFC2}" name="Port of discharge 目的港"/>
-    <tableColumn id="15" xr3:uid="{2A746044-8094-484F-8BEB-2376DCF69328}" name="Volume 材積"/>
-    <tableColumn id="16" xr3:uid="{EC23CB2D-E73E-4C45-9680-00F81B290105}" name="Vessel 船名"/>
-    <tableColumn id="17" xr3:uid="{AFD81601-A584-4AAB-A25A-A78FF380DD61}" name="Container no. 貨櫃號碼"/>
-    <tableColumn id="18" xr3:uid="{0E2211E7-F766-460E-8F3A-283258AFA43C}" name="Shipper 出貨方"/>
-    <tableColumn id="19" xr3:uid="{291B07E0-A001-4791-9A46-5D3932535943}" name="原幣別"/>
-    <tableColumn id="20" xr3:uid="{FF0BAE99-1E52-4A96-B437-B3A831919204}" name="匯率 (1 USD = ?)" dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{309D94C8-E3ED-4AB7-B3AB-F4367BADF89E}" name="AMOUNT (USD)" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{89D6CA72-8F1A-44C7-90FF-A5C2FB30EE74}" name="VAT (USD)" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{6560E217-2B8D-4196-B092-807849C1B884}" name="費用大類"/>
-    <tableColumn id="24" xr3:uid="{4C6D25CC-D09C-4012-88D6-9B4C92101767}" name="費用項目 (標準化)"/>
-    <tableColumn id="25" xr3:uid="{6D37DCBA-7748-48AE-A584-D7CF25E74257}" name="國家"/>
-    <tableColumn id="26" xr3:uid="{6AC9FB6C-E0D3-4244-8656-DBBC06863248}" name="年" dataDxfId="1"/>
-    <tableColumn id="27" xr3:uid="{BDF50658-DD5B-469D-A343-E4A12E086F31}" name="季"/>
-    <tableColumn id="28" xr3:uid="{0B14CEBA-2EDD-4856-9730-46E12AB03B2D}" name="月" dataDxfId="0"/>
-    <tableColumn id="29" xr3:uid="{66C4426A-E3F0-4263-A53C-240A63B35842}" name="年月"/>
-    <tableColumn id="30" xr3:uid="{12C92592-2224-40D9-B952-BFDD0F3D38D8}" name="航線"/>
-    <tableColumn id="31" xr3:uid="{86511CC8-F772-4916-8B10-BF0D65DC5803}" name="來源資料夾"/>
-    <tableColumn id="32" xr3:uid="{C9B65C0A-5B6D-4544-B18F-E5F93EF5FAA7}" name="來源檔案"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F8FF43C-74BD-4E61-9AC8-FFC40299264F}" name="明細表" displayName="明細表" ref="A1:AQ2" totalsRowShown="0">
+  <autoFilter ref="A1:AQ2" xr:uid="{4F8FF43C-74BD-4E61-9AC8-FFC40299264F}"/>
+  <tableColumns count="43">
+    <tableColumn id="1" xr3:uid="{A9CA7183-3A51-4D9A-AD4E-F97425C8DD54}" name="INVOICE DATE 發票日期" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A31B069C-D97D-485B-BA8C-E136A4EAAD45}" name="INVOICE NO 發票號碼"/>
+    <tableColumn id="3" xr3:uid="{9593EB8D-EA49-41F9-8DB9-B83CF42C55F0}" name="SUPPLIER 供應商名稱"/>
+    <tableColumn id="4" xr3:uid="{F1349514-97BE-4435-85BD-0D3D1AFDFAA3}" name="CONSIGNEE 集團公司名稱"/>
+    <tableColumn id="5" xr3:uid="{41DE48B6-317A-49FC-9982-494100567D4B}" name="Description 費用名稱"/>
+    <tableColumn id="6" xr3:uid="{9ADBC217-8563-460C-8702-7C200E5A2433}" name="AMOUNT 金額" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{6B2CE3EE-ACED-44E4-B80F-DBF9EF15FCC4}" name="VAT 稅額" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{856A8678-707B-420E-BE51-60FE1887DAC6}" name="Order No."/>
+    <tableColumn id="9" xr3:uid="{C4DF4891-9C43-4724-9A25-59115F8C882C}" name="Arrive Date 到達日" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{E11077E5-5552-428A-A9CE-5350CFE1BE88}" name="on board date 開船日" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{C25CEAE0-B56C-407C-9B1F-CB6657FAEE2F}" name="B/L NO. 提單號碼"/>
+    <tableColumn id="12" xr3:uid="{937A83E5-4290-4403-A3C4-B3E249F535B9}" name="MBL NO. 主提單號碼"/>
+    <tableColumn id="13" xr3:uid="{CFDCAE64-3B3D-434B-83F4-9F9DBC1D6EE6}" name="Port of Loading 啟運港"/>
+    <tableColumn id="14" xr3:uid="{F818B2D5-C812-47A6-9419-DBC964C8A326}" name="Port of discharge 目的港"/>
+    <tableColumn id="15" xr3:uid="{9AB73CBD-A300-474E-B799-F2C6E8126B17}" name="Volume 材積"/>
+    <tableColumn id="16" xr3:uid="{1CDBE89E-123C-4D06-A8D3-8180AB65A4F7}" name="Vessel 船名"/>
+    <tableColumn id="17" xr3:uid="{1C137FDB-B7FF-481C-930A-63873DE21D35}" name="Container no. 貨櫃號碼"/>
+    <tableColumn id="18" xr3:uid="{D77E18E5-70F8-4FE4-9DE6-9177D86625F9}" name="Shipper 出貨方"/>
+    <tableColumn id="19" xr3:uid="{B0DF156C-54A7-415B-9312-4AEA4A93D01D}" name="原幣別"/>
+    <tableColumn id="20" xr3:uid="{C7EF7F4A-40A0-4411-A7CB-F8F26F9BAB04}" name="匯率 (1 USD = ?)" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{83DE1BF1-3FC9-4F57-8FDF-80799ECDFD72}" name="AMOUNT (USD)" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{C4C0A3F4-06C2-47A7-ACC8-E2260EF7D54A}" name="VAT (USD)" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{ED3FDCBA-48AF-4E10-A456-A6B78DC50164}" name="費用大類"/>
+    <tableColumn id="24" xr3:uid="{6DE1AB2C-9CE1-4F6D-AD92-203D5A225CC6}" name="費用項目 (標準化)"/>
+    <tableColumn id="25" xr3:uid="{9C54050F-E2E6-460D-A867-7FC03DDB35F4}" name="國家"/>
+    <tableColumn id="26" xr3:uid="{A4CEA04A-57E8-43D4-8EDA-3C59B04AD34C}" name="年" dataDxfId="11"/>
+    <tableColumn id="27" xr3:uid="{68E520B4-ADE0-4CC2-99A6-A357188AB4AA}" name="季"/>
+    <tableColumn id="28" xr3:uid="{A646C4D7-B49C-41CC-9240-894E081FC79C}" name="月" dataDxfId="10"/>
+    <tableColumn id="29" xr3:uid="{7FFCD647-F574-4529-8BC5-FFAA430AA45C}" name="年月"/>
+    <tableColumn id="30" xr3:uid="{E8F7F3C9-A920-421A-9AD8-C1D766AEFE41}" name="航線"/>
+    <tableColumn id="31" xr3:uid="{42630F62-ABDE-4CD7-BB01-BE881F7CA706}" name="運送型態"/>
+    <tableColumn id="32" xr3:uid="{3A55A369-A8CC-48B3-BDC7-CD5716CA3B30}" name="20GP 櫃數" dataDxfId="9"/>
+    <tableColumn id="33" xr3:uid="{7F0016BE-D59E-4149-B772-59C678F00E0A}" name="40GP 櫃數" dataDxfId="8"/>
+    <tableColumn id="34" xr3:uid="{9D3F1F7E-E738-4EE8-B81E-78C0FEB44731}" name="40HC 櫃數" dataDxfId="7"/>
+    <tableColumn id="35" xr3:uid="{499CCFC7-EFC7-41A8-9511-99AF44520708}" name="45HC 櫃數" dataDxfId="6"/>
+    <tableColumn id="36" xr3:uid="{B07CDFC0-658B-48A4-A9FF-C86F0280A22C}" name="TEU" dataDxfId="5"/>
+    <tableColumn id="37" xr3:uid="{856E1CF9-DCDC-4F59-BBF4-43D01AC04A73}" name="CBM" dataDxfId="4"/>
+    <tableColumn id="38" xr3:uid="{7987076F-EB2C-4D3F-B94A-9FDA7D706C1E}" name="重量 KG" dataDxfId="3"/>
+    <tableColumn id="39" xr3:uid="{8EE9B9A8-49C7-4F8B-8D3F-18D4F763123C}" name="FCL 費用 (USD)" dataDxfId="2"/>
+    <tableColumn id="40" xr3:uid="{7524FC64-5F5B-4903-8995-11356D0102C3}" name="LCL 費用 (USD)" dataDxfId="1"/>
+    <tableColumn id="41" xr3:uid="{4B66E724-123C-4C61-949F-83B7D1823F96}" name="發票張數" dataDxfId="0"/>
+    <tableColumn id="42" xr3:uid="{1EE16B36-BFA7-4D26-BA5A-527B2875D63B}" name="來源資料夾"/>
+    <tableColumn id="43" xr3:uid="{97995065-B6F9-42BC-931A-0E4F785F6DA9}" name="來源檔案"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6A1F987-19AD-4445-9D70-DADD9A840637}" name="讀取失敗表" displayName="讀取失敗表" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2" xr:uid="{A6A1F987-19AD-4445-9D70-DADD9A840637}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A8F817F-B4CF-4ACA-A96A-0F1C860BAA4C}" name="讀取失敗表" displayName="讀取失敗表" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{2A8F817F-B4CF-4ACA-A96A-0F1C860BAA4C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{01A136F4-AF14-4B40-86F0-778E527BFE53}" name="檔案"/>
-    <tableColumn id="2" xr3:uid="{1AFE1804-B682-42F1-92BD-3FED69F0BF95}" name="原因"/>
+    <tableColumn id="1" xr3:uid="{FDAE397B-B2A2-44D1-8E2F-CE32E53BD2C5}" name="檔案"/>
+    <tableColumn id="2" xr3:uid="{7F47CB50-A78D-4941-AF88-DF8D13E0DD9E}" name="原因"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5603,98 +10360,167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5045FB-E292-48A2-8909-3E538A8E2A78}">
-  <dimension ref="A1:A2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39557176-3840-4E1D-A1DC-4632C2405308}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="21.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>46</v>
       </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>47</v>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CFC6FA-32EF-4237-8878-4A91FC88B10A}">
-  <dimension ref="A1:C7"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DBDB70-5572-4EF9-A6D7-E091B496893C}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>35</v>
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="7">
-        <v>2026</v>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="8">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="E5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5704,59 +10530,91 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7ED90F-661A-4FDC-AF12-964DA206BB8C}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B1CF52-BA00-49BE-A1A5-6ACF8EF6B355}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>40</v>
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5">
         <v>0</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5766,70 +10624,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF6E947-2993-443D-B995-6F0148935125}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5827ED3E-1C4D-4461-9F5B-2170978C4218}">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CEE2C0-69FA-4ABA-9E33-33E2A318D707}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5838,21 +10634,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>42</v>
+      <c r="A1" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>36</v>
+      <c r="A3" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -5860,7 +10656,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -5872,9 +10668,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4566F57E-1438-4CA7-A9CD-A7DF17740179}">
-  <dimension ref="A1:AF2"/>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD900A9-5DA0-4092-92F8-A1CDCAD84FB5}">
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -5899,10 +10695,12 @@
     <col min="22" max="22" width="13.6328125" customWidth="1"/>
     <col min="23" max="23" width="12.6328125" customWidth="1"/>
     <col min="24" max="24" width="14.6328125" customWidth="1"/>
-    <col min="25" max="32" width="12.6328125" customWidth="1"/>
+    <col min="25" max="38" width="12.6328125" customWidth="1"/>
+    <col min="39" max="40" width="16.6328125" customWidth="1"/>
+    <col min="41" max="43" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5999,22 +10797,55 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>46023</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -6023,7 +10854,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1">
         <v>46023</v>
@@ -6032,31 +10863,31 @@
         <v>46023</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="R2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
@@ -6068,34 +10899,67 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="X2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Y2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Z2" s="4">
         <v>2026</v>
       </c>
       <c r="AA2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="AB2" s="4">
         <v>1</v>
       </c>
       <c r="AC2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="AD2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AE2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6107,8 +10971,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9193A0-50DF-4640-BC07-29C67136B4B6}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF88AADA-2DC3-4965-92F6-06BB5297C9BA}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
@@ -6117,18 +10981,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6138,4 +11002,490 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F87E89-B9D6-496B-833D-C4E6D93FCFEA}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="21.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7911282-98EC-4747-A8C0-ED1C0EC2A384}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184EBCD5-6D98-4673-9274-0916EEDF1A04}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86EBA47-545B-459D-9CEC-4DDF1339D2AD}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601CF029-841A-4281-A37A-DC79821D26E5}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="12">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3F26B5-E571-48A5-98D0-6FA8C2E9C782}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7A977D-83BB-402A-91E4-D23BB940CE9A}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6ECF98-E59A-4847-852F-4E406C5B81F9}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/expense_dashboard/templates/pivot_template.xlsx
+++ b/expense_dashboard/templates/pivot_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\資誠claude code專案資料夾\invoice_excel_mapping\expense_dashboard\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9F9F94D-C939-4785-B8C2-7C59CDEE48B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87FBD4DE-AF02-46ED-99B1-9E511964941A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15465" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{2573DD42-5528-4BE5-8CB9-540C2F60DDE8}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8250" xr2:uid="{B1ED41E5-B6B8-4D84-ADBB-5CAC90EBF1FF}"/>
   </bookViews>
   <sheets>
     <sheet name="儀表板_總覽" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="24" r:id="rId15"/>
+    <pivotCache cacheId="23" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="77">
   <si>
     <t>INVOICE DATE 發票日期</t>
   </si>
@@ -227,9 +227,6 @@
     <t>每 TEU 成本 (USD)</t>
   </si>
   <si>
-    <t>每 CBM 成本 (USD)</t>
-  </si>
-  <si>
     <t>每月 × 費用大類 (USD)</t>
   </si>
   <si>
@@ -275,7 +272,7 @@
     <t>45HC</t>
   </si>
   <si>
-    <t>單位成本 (供應商)：每 TEU = FCL 費用 / TEU，每 CBM = LCL 費用 / CBM</t>
+    <t>單位成本 (供應商)：每 TEU 成本 = FCL 費用 / TEU</t>
   </si>
   <si>
     <t>FCL 費用</t>
@@ -695,7 +692,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A628-4260-B7DC-9BA4B2BA9E1D}"/>
+              <c16:uniqueId val="{00000001-8623-4131-94D1-CC8B51B90094}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -709,11 +706,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="449671504"/>
-        <c:axId val="449672464"/>
+        <c:axId val="674074896"/>
+        <c:axId val="674075856"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="449671504"/>
+        <c:axId val="674074896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -756,7 +753,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449672464"/>
+        <c:crossAx val="674075856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -764,7 +761,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="449672464"/>
+        <c:axId val="674075856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -815,7 +812,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449671504"/>
+        <c:crossAx val="674074896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1086,7 +1083,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FD59-4D3C-83FD-40873E6743F3}"/>
+              <c16:uniqueId val="{00000001-984E-4F93-970C-E18CD882E6E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1099,11 +1096,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="449667664"/>
-        <c:axId val="449671024"/>
+        <c:axId val="1027693056"/>
+        <c:axId val="1027694016"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="449667664"/>
+        <c:axId val="1027693056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1146,7 +1143,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449671024"/>
+        <c:crossAx val="1027694016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1154,7 +1151,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="449671024"/>
+        <c:axId val="1027694016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1205,7 +1202,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449667664"/>
+        <c:crossAx val="1027693056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1473,7 +1470,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-16D9-4472-8C6C-DAA4FF5C3977}"/>
+              <c16:uniqueId val="{00000001-010B-4921-9094-23CB4E67B6D3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1487,11 +1484,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="449671984"/>
-        <c:axId val="449672944"/>
+        <c:axId val="1027693536"/>
+        <c:axId val="1027694496"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="449671984"/>
+        <c:axId val="1027693536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1534,7 +1531,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449672944"/>
+        <c:crossAx val="1027694496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1542,7 +1539,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="449672944"/>
+        <c:axId val="1027694496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1593,7 +1590,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449671984"/>
+        <c:crossAx val="1027693536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1862,7 +1859,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-52BF-4946-8934-AF0DC5CEFBEE}"/>
+              <c16:uniqueId val="{00000001-21C4-4159-A8F6-228D692749E4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1876,11 +1873,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="449669104"/>
-        <c:axId val="449673904"/>
+        <c:axId val="1030306000"/>
+        <c:axId val="1030305520"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="449669104"/>
+        <c:axId val="1030306000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1923,7 +1920,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449673904"/>
+        <c:crossAx val="1030305520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1931,7 +1928,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="449673904"/>
+        <c:axId val="1030305520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1982,7 +1979,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="449669104"/>
+        <c:crossAx val="1030306000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2407,7 +2404,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0506-4FCE-8E87-E08476429540}"/>
+              <c16:uniqueId val="{00000001-BFEE-47BB-AE56-BF77AB52ED8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2460,7 +2457,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0506-4FCE-8E87-E08476429540}"/>
+              <c16:uniqueId val="{00000002-BFEE-47BB-AE56-BF77AB52ED8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2513,7 +2510,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0506-4FCE-8E87-E08476429540}"/>
+              <c16:uniqueId val="{00000003-BFEE-47BB-AE56-BF77AB52ED8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2566,7 +2563,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-0506-4FCE-8E87-E08476429540}"/>
+              <c16:uniqueId val="{00000004-BFEE-47BB-AE56-BF77AB52ED8B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2580,11 +2577,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="451308528"/>
-        <c:axId val="451304688"/>
+        <c:axId val="1030306480"/>
+        <c:axId val="1030304080"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="451308528"/>
+        <c:axId val="1030306480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2627,7 +2624,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451304688"/>
+        <c:crossAx val="1030304080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2635,7 +2632,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="451304688"/>
+        <c:axId val="1030304080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2686,7 +2683,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451308528"/>
+        <c:crossAx val="1030306480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2955,7 +2952,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4126-483E-8ABA-9878AEA140FE}"/>
+              <c16:uniqueId val="{00000001-43F0-42D5-B5F5-20D09BAF88CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2968,11 +2965,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="451302768"/>
-        <c:axId val="451306128"/>
+        <c:axId val="1030416752"/>
+        <c:axId val="1030417232"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="451302768"/>
+        <c:axId val="1030416752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3015,7 +3012,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451306128"/>
+        <c:crossAx val="1030417232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3023,7 +3020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="451306128"/>
+        <c:axId val="1030417232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3074,7 +3071,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451302768"/>
+        <c:crossAx val="1030416752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3343,7 +3340,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-35CF-4DF1-9C43-DCB9D8913420}"/>
+              <c16:uniqueId val="{00000001-5982-4524-8D7D-BBCF0D8E78D8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3357,11 +3354,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="451304208"/>
-        <c:axId val="451307088"/>
+        <c:axId val="1030594944"/>
+        <c:axId val="1030593504"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="451304208"/>
+        <c:axId val="1030594944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3404,7 +3401,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451307088"/>
+        <c:crossAx val="1030593504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3412,7 +3409,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="451307088"/>
+        <c:axId val="1030593504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3463,7 +3460,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451304208"/>
+        <c:crossAx val="1030594944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7363,16 +7360,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7381,7 +7378,7 @@
             <xdr:cNvPr id="2" name="國家">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F05E6B7-4F6C-D798-11D0-A550272068E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C4F7E3-F934-42C0-A35F-F3926795E16D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7408,8 +7405,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7441,16 +7438,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7459,7 +7456,7 @@
             <xdr:cNvPr id="3" name="SUPPLIER 供應商名稱">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBF1249-1F28-158C-71F1-3D808C903872}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{723C57D3-1451-5411-0345-1E405F83561D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7486,8 +7483,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7519,16 +7516,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7537,7 +7534,7 @@
             <xdr:cNvPr id="4" name="年">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5BEF47-50A2-0145-B1B9-12026E161CC5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70B76759-BDAB-D4B1-1CBE-DC311B41F46C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7564,8 +7561,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7597,16 +7594,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7615,7 +7612,7 @@
             <xdr:cNvPr id="5" name="費用大類">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FABA66A-E3DD-8254-7E91-7C1F49DA0AF3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E79069B0-8FC0-03DA-EFAD-40D54A7FBCBA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7642,8 +7639,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7676,22 +7673,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>206375</xdr:rowOff>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="6" name="圖表 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1800119B-3544-96BC-3787-3CB88ED7F960}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB1560A-DAD6-D3A1-8370-BC61F497F796}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7711,23 +7708,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>206375</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="7" name="圖表 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF58B2E-F345-9860-7B62-E86C8BB41DB3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F14A9801-940C-8BB5-BA9C-CEA24A1B9577}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7748,22 +7745,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>127000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>136525</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="8" name="圖表 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{392793D5-4B66-8115-E111-C17CBBE67BF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99196CB6-DB60-8898-F07A-E5FD06CE46BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7783,23 +7780,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>136525</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="9" name="圖表 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA60F51-3035-B823-98BC-B39CE8D58A21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAE664ED-D649-BF2C-021D-0652B52CC3C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7824,16 +7821,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7842,7 +7839,7 @@
             <xdr:cNvPr id="2" name="國家 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03B46CDE-A4A5-247D-6411-D8387B7D5D85}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D6F6C72-89BC-C5D0-94E6-8B197099B8EE}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7869,8 +7866,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7902,16 +7899,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7920,7 +7917,7 @@
             <xdr:cNvPr id="3" name="SUPPLIER 供應商名稱 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8320BE77-99F4-B19A-E887-89F5A021FAD9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A573EF15-2615-EDFD-CAAB-BA3A0440A90D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7947,8 +7944,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7980,16 +7977,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7998,7 +7995,7 @@
             <xdr:cNvPr id="4" name="年 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB6895C0-FE06-A2AC-56C4-62B791C9E935}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE252631-4882-2DBA-7251-5D4344287141}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8025,8 +8022,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8058,16 +8055,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -8076,7 +8073,7 @@
             <xdr:cNvPr id="5" name="費用大類 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2E75C2-19FB-364A-DEF7-B04213492AF1}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDC8CDC-2125-9EF3-538B-13D781BFB58E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8103,8 +8100,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6597650" y="2292350"/>
-              <a:ext cx="1828800" cy="2336797"/>
+              <a:off x="3486150" y="825500"/>
+              <a:ext cx="1828800" cy="2333622"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8137,22 +8134,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>127000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="6" name="圖表 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C686782D-D613-6326-BC7D-0DD65ECD041D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E379D500-61C7-D8E2-3743-2569CD0141BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8175,20 +8172,20 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>50800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="7" name="圖表 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B61F53FA-1335-2852-4BD5-43B8D9CB6815}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6886A44F-77A9-793A-488B-9A4E6C40758F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8209,22 +8206,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>193675</xdr:rowOff>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="8" name="圖表 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{922764A3-0828-E8A8-4207-1A675C8FFD63}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43BCC219-213B-1053-DE75-E33CC555D87E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8246,11 +8243,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="" refreshedDate="46322.714291782409" missingItemsLimit="0" createdVersion="5" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{2116379A-D551-4788-BFB1-F68BB7109533}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="" refreshedDate="46322.77512395833" missingItemsLimit="0" createdVersion="5" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{D7BD60B3-608F-462F-9C70-C8E8018E3F92}">
   <cacheSource type="worksheet">
     <worksheetSource name="明細表"/>
   </cacheSource>
-  <cacheFields count="45">
+  <cacheFields count="44">
     <cacheField name="INVOICE DATE 發票日期" numFmtId="176">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-01-02T00:00:00"/>
     </cacheField>
@@ -8397,20 +8394,19 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="每TEU成本" numFmtId="0" formula="'FCL 費用 (USD)'/TEU" databaseField="0"/>
-    <cacheField name="每CBM成本" numFmtId="0" formula="'LCL 費用 (USD)'/CBM" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="341430193"/>
+      <x14:pivotCacheDefinition pivotCacheId="1513859983"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59441AF4-8125-40B3-AB76-EFEC9D6613C4}" name="PT_KPI" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A4:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="45">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA7B781B-5EB8-458D-876A-C20DCAE10F3A}" name="PT_KPI" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:E5" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -8475,7 +8471,6 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowItems count="1">
     <i/>
@@ -8483,7 +8478,7 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -8499,17 +8494,13 @@
     <i i="4">
       <x v="4"/>
     </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
   </colItems>
-  <dataFields count="6">
+  <dataFields count="5">
     <dataField name="USD 金額" fld="20" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="發票數" fld="40" baseField="0" baseItem="0" numFmtId="3"/>
     <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
     <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
     <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
-    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -8524,9 +8515,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5DAA4AFA-A314-4EB1-B87A-1A30B3AC445C}" name="PT_單位成本_航線" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="45">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4CC979A-20FB-46F6-843C-3EA4CD742EB6}" name="PT_單位成本_航線" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -8604,7 +8595,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -8621,7 +8611,7 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -8637,17 +8627,13 @@
     <i i="4">
       <x v="4"/>
     </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
   </colItems>
-  <dataFields count="6">
+  <dataFields count="5">
     <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
     <dataField name="FCL 費用" fld="38" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="LCL 費用" fld="39" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
-    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
@@ -8671,9 +8657,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70DDBC77-36D9-4F62-BB0B-F2342A2C38CB}" name="PT_航線" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{352D2B73-A9DB-49E0-AB45-5A8A01900519}" name="PT_航線" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -8751,7 +8737,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -8804,9 +8789,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74879E4B-480A-4C12-8C3E-7BAC3D533B66}" name="PT_每月費用大類" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87320E55-0C94-498B-8782-8BE87F4BA99B}" name="PT_每月費用大類" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -8875,7 +8860,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -8930,9 +8914,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EF9368FE-44FB-4A88-B132-5308202E4733}" name="PT_年度比較" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1B3B69AA-276D-4BD6-8CE8-FE0E882770BD}" name="PT_年度比較" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -9001,7 +8985,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9056,9 +9039,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DF1B6232-FF2D-4EE7-BD7D-E8805FFE5E60}" name="PT_供應商排名" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D16DD49-0816-4F2B-B4AA-7E434CCE31B4}" name="PT_供應商排名" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -9131,7 +9114,6 @@
     <pivotField dataField="1" numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9177,9 +9159,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8520181-2AA9-49B3-8BE3-010C13E278EF}" name="PT_供應商月份" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5002E066-63C2-42B0-8CCB-F73BA696CD41}" name="PT_供應商月份" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -9248,7 +9230,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
@@ -9307,9 +9288,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{79CE60CB-B5CC-47AF-ACA9-21415ABBEEC9}" name="PT_費用大類" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{20FC6816-DB04-4556-9F1E-541D42A45C12}" name="PT_費用大類" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
@@ -9382,7 +9363,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9437,9 +9417,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B92C70EA-5B5A-4B5B-8511-52393FE7A533}" name="PT_集團公司" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DBA43051-FB48-406A-85F6-8526F98CF406}" name="PT_集團公司" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -9517,7 +9497,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9572,9 +9551,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37530A12-3C84-4342-8793-715D8BF9AA36}" name="PT_運量" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55DF292A-7842-471D-B09B-DDBB9CB518EF}" name="PT_運量" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:E5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="45">
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -9643,7 +9622,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9731,9 +9709,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09538EE3-167C-43D0-B6EF-83A93C85EE91}" name="PT_單位成本_供應商" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="45">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{29FD5C92-FBC7-4E1A-8592-A8CAA1DBBCA7}" name="PT_單位成本_供應商" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" errorCaption="-" showError="1" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="44">
     <pivotField numFmtId="176" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -9806,7 +9784,6 @@
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -9823,7 +9800,7 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -9839,17 +9816,13 @@
     <i i="4">
       <x v="4"/>
     </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
   </colItems>
-  <dataFields count="6">
+  <dataFields count="5">
     <dataField name="FCL 費用" fld="38" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="TEU 數" fld="35" baseField="0" baseItem="0" numFmtId="3"/>
     <dataField name="每 TEU 成本 (USD)" fld="43" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="LCL 費用" fld="39" baseField="0" baseItem="0" numFmtId="4"/>
     <dataField name="CBM 數" fld="36" baseField="0" baseItem="0" numFmtId="178"/>
-    <dataField name="每 CBM 成本 (USD)" fld="44" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -9864,7 +9837,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_國家" xr10:uid="{0C6924CD-8AA9-4635-9554-748C1AFD8971}" sourceName="國家">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_國家" xr10:uid="{DE274A62-6C78-4660-8FA4-1100D84FD0AA}" sourceName="國家">
   <pivotTables>
     <pivotTable tabId="1" name="PT_KPI"/>
     <pivotTable tabId="4" name="PT_每月費用大類"/>
@@ -9879,7 +9852,7 @@
     <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="341430193">
+    <tabular pivotCacheId="1513859983">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -9889,7 +9862,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_SUPPLIER_供應商名稱" xr10:uid="{FF7C1E86-ABD8-40ED-927B-F83DD9827A05}" sourceName="SUPPLIER 供應商名稱">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_SUPPLIER_供應商名稱" xr10:uid="{DEBCBBDB-3CF4-4EA7-9662-2F89E245E51D}" sourceName="SUPPLIER 供應商名稱">
   <pivotTables>
     <pivotTable tabId="1" name="PT_KPI"/>
     <pivotTable tabId="4" name="PT_每月費用大類"/>
@@ -9904,7 +9877,7 @@
     <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="341430193">
+    <tabular pivotCacheId="1513859983">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -9914,7 +9887,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_年" xr10:uid="{F2556E91-E61A-4BB2-BC63-CDBBF5385AFB}" sourceName="年">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_年" xr10:uid="{B485A9CD-65D1-469B-880D-875078AC22C8}" sourceName="年">
   <pivotTables>
     <pivotTable tabId="1" name="PT_KPI"/>
     <pivotTable tabId="4" name="PT_每月費用大類"/>
@@ -9929,7 +9902,7 @@
     <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="341430193">
+    <tabular pivotCacheId="1513859983">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -9939,7 +9912,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_費用大類" xr10:uid="{D590E2D3-9E31-4AA7-88B3-D9194AC10CF4}" sourceName="費用大類">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_費用大類" xr10:uid="{25431627-1E18-460B-AFED-5447F77CCC55}" sourceName="費用大類">
   <pivotTables>
     <pivotTable tabId="1" name="PT_KPI"/>
     <pivotTable tabId="4" name="PT_每月費用大類"/>
@@ -9954,7 +9927,7 @@
     <pivotTable tabId="13" name="PT_航線"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="341430193">
+    <tabular pivotCacheId="1513859983">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -9965,80 +9938,80 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="國家" xr10:uid="{6C0A8404-C2F8-42F6-A0D8-D97631E7AF5C}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
-  <slicer name="SUPPLIER 供應商名稱" xr10:uid="{3EC8ABB1-421E-4EBD-B770-4E091E13B5A6}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
-  <slicer name="年" xr10:uid="{9F12D052-DC10-416E-953D-CDD16B831657}" cache="Slicer_年" caption="年" rowHeight="220133"/>
-  <slicer name="費用大類" xr10:uid="{1804D4D9-A5A9-48CD-A28B-A817A42D98D7}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
+  <slicer name="國家" xr10:uid="{563069CA-F2B3-45E7-9AF6-1F4E8C9BB79E}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
+  <slicer name="SUPPLIER 供應商名稱" xr10:uid="{8AF8C9EA-A4BB-41E7-88C6-B5AF8F7119AE}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
+  <slicer name="年" xr10:uid="{2572516B-3823-4D0E-B717-EBF539C3A453}" cache="Slicer_年" caption="年" rowHeight="220133"/>
+  <slicer name="費用大類" xr10:uid="{D33DF2FE-78C0-4083-A03F-05640B5A2678}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
 </slicers>
 </file>
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="國家 1" xr10:uid="{969B2AB5-429F-42A9-9902-307CD038B2DC}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
-  <slicer name="SUPPLIER 供應商名稱 1" xr10:uid="{AE1CD86A-2D57-4342-AD0D-552FB14B054D}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
-  <slicer name="年 1" xr10:uid="{1BCAE515-77E1-46CA-8EB2-722A022384D4}" cache="Slicer_年" caption="年" rowHeight="220133"/>
-  <slicer name="費用大類 1" xr10:uid="{4C065B2C-0853-40D9-944D-EB8FB1A19CA8}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
+  <slicer name="國家 1" xr10:uid="{9131DC52-1304-4539-8785-B95206DBB706}" cache="Slicer_國家" caption="國家" rowHeight="220133"/>
+  <slicer name="SUPPLIER 供應商名稱 1" xr10:uid="{9CF37B31-4866-4687-8CB7-8DDD8C90AFEB}" cache="Slicer_SUPPLIER_供應商名稱" caption="SUPPLIER 供應商名稱" rowHeight="220133"/>
+  <slicer name="年 1" xr10:uid="{C522B6CE-3538-4A1E-8C49-E4D7CC087B5F}" cache="Slicer_年" caption="年" rowHeight="220133"/>
+  <slicer name="費用大類 1" xr10:uid="{0007A081-F8CC-4DD2-9095-87A8E0F48137}" cache="Slicer_費用大類" caption="費用大類" rowHeight="220133"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4F8FF43C-74BD-4E61-9AC8-FFC40299264F}" name="明細表" displayName="明細表" ref="A1:AQ2" totalsRowShown="0">
-  <autoFilter ref="A1:AQ2" xr:uid="{4F8FF43C-74BD-4E61-9AC8-FFC40299264F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{536E6309-83E0-4CC2-A4E0-7277AB1983C8}" name="明細表" displayName="明細表" ref="A1:AQ2" totalsRowShown="0">
+  <autoFilter ref="A1:AQ2" xr:uid="{536E6309-83E0-4CC2-A4E0-7277AB1983C8}"/>
   <tableColumns count="43">
-    <tableColumn id="1" xr3:uid="{A9CA7183-3A51-4D9A-AD4E-F97425C8DD54}" name="INVOICE DATE 發票日期" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{A31B069C-D97D-485B-BA8C-E136A4EAAD45}" name="INVOICE NO 發票號碼"/>
-    <tableColumn id="3" xr3:uid="{9593EB8D-EA49-41F9-8DB9-B83CF42C55F0}" name="SUPPLIER 供應商名稱"/>
-    <tableColumn id="4" xr3:uid="{F1349514-97BE-4435-85BD-0D3D1AFDFAA3}" name="CONSIGNEE 集團公司名稱"/>
-    <tableColumn id="5" xr3:uid="{41DE48B6-317A-49FC-9982-494100567D4B}" name="Description 費用名稱"/>
-    <tableColumn id="6" xr3:uid="{9ADBC217-8563-460C-8702-7C200E5A2433}" name="AMOUNT 金額" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{6B2CE3EE-ACED-44E4-B80F-DBF9EF15FCC4}" name="VAT 稅額" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{856A8678-707B-420E-BE51-60FE1887DAC6}" name="Order No."/>
-    <tableColumn id="9" xr3:uid="{C4DF4891-9C43-4724-9A25-59115F8C882C}" name="Arrive Date 到達日" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{E11077E5-5552-428A-A9CE-5350CFE1BE88}" name="on board date 開船日" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{C25CEAE0-B56C-407C-9B1F-CB6657FAEE2F}" name="B/L NO. 提單號碼"/>
-    <tableColumn id="12" xr3:uid="{937A83E5-4290-4403-A3C4-B3E249F535B9}" name="MBL NO. 主提單號碼"/>
-    <tableColumn id="13" xr3:uid="{CFDCAE64-3B3D-434B-83F4-9F9DBC1D6EE6}" name="Port of Loading 啟運港"/>
-    <tableColumn id="14" xr3:uid="{F818B2D5-C812-47A6-9419-DBC964C8A326}" name="Port of discharge 目的港"/>
-    <tableColumn id="15" xr3:uid="{9AB73CBD-A300-474E-B799-F2C6E8126B17}" name="Volume 材積"/>
-    <tableColumn id="16" xr3:uid="{1CDBE89E-123C-4D06-A8D3-8180AB65A4F7}" name="Vessel 船名"/>
-    <tableColumn id="17" xr3:uid="{1C137FDB-B7FF-481C-930A-63873DE21D35}" name="Container no. 貨櫃號碼"/>
-    <tableColumn id="18" xr3:uid="{D77E18E5-70F8-4FE4-9DE6-9177D86625F9}" name="Shipper 出貨方"/>
-    <tableColumn id="19" xr3:uid="{B0DF156C-54A7-415B-9312-4AEA4A93D01D}" name="原幣別"/>
-    <tableColumn id="20" xr3:uid="{C7EF7F4A-40A0-4411-A7CB-F8F26F9BAB04}" name="匯率 (1 USD = ?)" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{83DE1BF1-3FC9-4F57-8FDF-80799ECDFD72}" name="AMOUNT (USD)" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{C4C0A3F4-06C2-47A7-ACC8-E2260EF7D54A}" name="VAT (USD)" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{ED3FDCBA-48AF-4E10-A456-A6B78DC50164}" name="費用大類"/>
-    <tableColumn id="24" xr3:uid="{6DE1AB2C-9CE1-4F6D-AD92-203D5A225CC6}" name="費用項目 (標準化)"/>
-    <tableColumn id="25" xr3:uid="{9C54050F-E2E6-460D-A867-7FC03DDB35F4}" name="國家"/>
-    <tableColumn id="26" xr3:uid="{A4CEA04A-57E8-43D4-8EDA-3C59B04AD34C}" name="年" dataDxfId="11"/>
-    <tableColumn id="27" xr3:uid="{68E520B4-ADE0-4CC2-99A6-A357188AB4AA}" name="季"/>
-    <tableColumn id="28" xr3:uid="{A646C4D7-B49C-41CC-9240-894E081FC79C}" name="月" dataDxfId="10"/>
-    <tableColumn id="29" xr3:uid="{7FFCD647-F574-4529-8BC5-FFAA430AA45C}" name="年月"/>
-    <tableColumn id="30" xr3:uid="{E8F7F3C9-A920-421A-9AD8-C1D766AEFE41}" name="航線"/>
-    <tableColumn id="31" xr3:uid="{42630F62-ABDE-4CD7-BB01-BE881F7CA706}" name="運送型態"/>
-    <tableColumn id="32" xr3:uid="{3A55A369-A8CC-48B3-BDC7-CD5716CA3B30}" name="20GP 櫃數" dataDxfId="9"/>
-    <tableColumn id="33" xr3:uid="{7F0016BE-D59E-4149-B772-59C678F00E0A}" name="40GP 櫃數" dataDxfId="8"/>
-    <tableColumn id="34" xr3:uid="{9D3F1F7E-E738-4EE8-B81E-78C0FEB44731}" name="40HC 櫃數" dataDxfId="7"/>
-    <tableColumn id="35" xr3:uid="{499CCFC7-EFC7-41A8-9511-99AF44520708}" name="45HC 櫃數" dataDxfId="6"/>
-    <tableColumn id="36" xr3:uid="{B07CDFC0-658B-48A4-A9FF-C86F0280A22C}" name="TEU" dataDxfId="5"/>
-    <tableColumn id="37" xr3:uid="{856E1CF9-DCDC-4F59-BBF4-43D01AC04A73}" name="CBM" dataDxfId="4"/>
-    <tableColumn id="38" xr3:uid="{7987076F-EB2C-4D3F-B94A-9FDA7D706C1E}" name="重量 KG" dataDxfId="3"/>
-    <tableColumn id="39" xr3:uid="{8EE9B9A8-49C7-4F8B-8D3F-18D4F763123C}" name="FCL 費用 (USD)" dataDxfId="2"/>
-    <tableColumn id="40" xr3:uid="{7524FC64-5F5B-4903-8995-11356D0102C3}" name="LCL 費用 (USD)" dataDxfId="1"/>
-    <tableColumn id="41" xr3:uid="{4B66E724-123C-4C61-949F-83B7D1823F96}" name="發票張數" dataDxfId="0"/>
-    <tableColumn id="42" xr3:uid="{1EE16B36-BFA7-4D26-BA5A-527B2875D63B}" name="來源資料夾"/>
-    <tableColumn id="43" xr3:uid="{97995065-B6F9-42BC-931A-0E4F785F6DA9}" name="來源檔案"/>
+    <tableColumn id="1" xr3:uid="{2279D1C9-56E6-42C2-A434-BD0015374A19}" name="INVOICE DATE 發票日期" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{6054866D-C469-4E79-8C74-B228A39AD5C2}" name="INVOICE NO 發票號碼"/>
+    <tableColumn id="3" xr3:uid="{D61CADDC-36E3-4951-9C18-171BDC55C930}" name="SUPPLIER 供應商名稱"/>
+    <tableColumn id="4" xr3:uid="{A1383D81-E9E1-4F26-8B55-106FB0CD5366}" name="CONSIGNEE 集團公司名稱"/>
+    <tableColumn id="5" xr3:uid="{359BFFE8-CA97-46E5-83A4-5FAB4D1FE3F3}" name="Description 費用名稱"/>
+    <tableColumn id="6" xr3:uid="{304CC7A2-2644-41E3-A479-2DC977672A68}" name="AMOUNT 金額" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{EE55F3C8-B2F5-4C7E-B946-5293B9A1A5B0}" name="VAT 稅額" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{F4DA8F10-3B94-4F06-B4AD-01E367E16D55}" name="Order No."/>
+    <tableColumn id="9" xr3:uid="{48DC066F-626A-4421-8C91-4467848E7325}" name="Arrive Date 到達日" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C9CCBD70-2EAD-4451-A487-463167C631D3}" name="on board date 開船日" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{C1EB9BF5-7D87-4501-891C-A6B9987FB667}" name="B/L NO. 提單號碼"/>
+    <tableColumn id="12" xr3:uid="{01886B00-D230-4B8A-B50E-CD5EED3D447F}" name="MBL NO. 主提單號碼"/>
+    <tableColumn id="13" xr3:uid="{02C098A7-6C68-4A1B-AF57-6013B20C39EC}" name="Port of Loading 啟運港"/>
+    <tableColumn id="14" xr3:uid="{B631DC02-35F6-48D3-AFC8-9F35124A67B4}" name="Port of discharge 目的港"/>
+    <tableColumn id="15" xr3:uid="{962A8104-C93C-4CB5-BF51-66B7AD414D8A}" name="Volume 材積"/>
+    <tableColumn id="16" xr3:uid="{8C92A904-5829-4AA1-886A-A2AF5762C400}" name="Vessel 船名"/>
+    <tableColumn id="17" xr3:uid="{0F6CC08A-58F1-4DE7-8FD3-2088C06159E8}" name="Container no. 貨櫃號碼"/>
+    <tableColumn id="18" xr3:uid="{D2CBB456-A5B4-4845-B597-F40B2E6E28FD}" name="Shipper 出貨方"/>
+    <tableColumn id="19" xr3:uid="{CF72DC69-6EEF-45CD-B04A-8264832AC232}" name="原幣別"/>
+    <tableColumn id="20" xr3:uid="{6F14B261-4022-4E4E-B655-ED2B683C8C52}" name="匯率 (1 USD = ?)" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{C5218551-411C-44DD-AE17-14C231D3E7B8}" name="AMOUNT (USD)" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{94F5E505-4CF5-4ECE-B734-372CB4C1DBEF}" name="VAT (USD)" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{4BB2868C-1154-4BAB-AEDD-FBD5B002079E}" name="費用大類"/>
+    <tableColumn id="24" xr3:uid="{5207E985-1F39-4D72-8DEB-2028B5B1C776}" name="費用項目 (標準化)"/>
+    <tableColumn id="25" xr3:uid="{73A91353-2C12-443C-84FC-E58A83587CCD}" name="國家"/>
+    <tableColumn id="26" xr3:uid="{342984DB-E9B9-49B1-9AA7-B745A8DD6122}" name="年" dataDxfId="11"/>
+    <tableColumn id="27" xr3:uid="{3FAB2159-E8ED-4D5D-B5C4-60B14CB4C4C9}" name="季"/>
+    <tableColumn id="28" xr3:uid="{4D72578A-EA6F-4EEB-8676-EA4F90882A7C}" name="月" dataDxfId="10"/>
+    <tableColumn id="29" xr3:uid="{2849F91A-B281-44CC-BE72-644BCEC1DBC6}" name="年月"/>
+    <tableColumn id="30" xr3:uid="{3947412B-C7CA-409A-A11A-0D7D50404917}" name="航線"/>
+    <tableColumn id="31" xr3:uid="{5D5BC8AC-0D57-44A2-95F8-B13CF46825DF}" name="運送型態"/>
+    <tableColumn id="32" xr3:uid="{01EAF0EF-FF37-4FB9-B13E-94BFC230FED8}" name="20GP 櫃數" dataDxfId="9"/>
+    <tableColumn id="33" xr3:uid="{4DE83C2E-A5D7-4502-908B-A7E5214971FF}" name="40GP 櫃數" dataDxfId="8"/>
+    <tableColumn id="34" xr3:uid="{3421175F-0DC6-4805-BFE3-F465D8751F10}" name="40HC 櫃數" dataDxfId="7"/>
+    <tableColumn id="35" xr3:uid="{8346C7F4-D522-43F8-A9F2-8B93C7CF74A4}" name="45HC 櫃數" dataDxfId="6"/>
+    <tableColumn id="36" xr3:uid="{1EA2CE0B-B5D0-49E7-858C-B56F1BEA5EB5}" name="TEU" dataDxfId="5"/>
+    <tableColumn id="37" xr3:uid="{05F6FC02-301A-4D43-B974-C2C1101ED33B}" name="CBM" dataDxfId="4"/>
+    <tableColumn id="38" xr3:uid="{7A5B4FC9-53C8-4985-B003-DDA293C25089}" name="重量 KG" dataDxfId="3"/>
+    <tableColumn id="39" xr3:uid="{8980DEB9-3DB4-464D-93B0-29B8CB4BE6EF}" name="FCL 費用 (USD)" dataDxfId="2"/>
+    <tableColumn id="40" xr3:uid="{48F30DED-4705-49A1-9255-BC63EE6B8AC0}" name="LCL 費用 (USD)" dataDxfId="1"/>
+    <tableColumn id="41" xr3:uid="{6297C168-D8BF-4970-88EB-4114662E20D1}" name="發票張數" dataDxfId="0"/>
+    <tableColumn id="42" xr3:uid="{F9300900-E87B-4A2A-B89A-86469DD712A5}" name="來源資料夾"/>
+    <tableColumn id="43" xr3:uid="{C29235AA-C97D-47FF-BD39-5DA44CD5F4E8}" name="來源檔案"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A8F817F-B4CF-4ACA-A96A-0F1C860BAA4C}" name="讀取失敗表" displayName="讀取失敗表" ref="A1:B2" totalsRowShown="0">
-  <autoFilter ref="A1:B2" xr:uid="{2A8F817F-B4CF-4ACA-A96A-0F1C860BAA4C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B19D9851-E119-4639-955E-9DC179B82AFF}" name="讀取失敗表" displayName="讀取失敗表" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{B19D9851-E119-4639-955E-9DC179B82AFF}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FDAE397B-B2A2-44D1-8E2F-CE32E53BD2C5}" name="檔案"/>
-    <tableColumn id="2" xr3:uid="{7F47CB50-A78D-4941-AF88-DF8D13E0DD9E}" name="原因"/>
+    <tableColumn id="1" xr3:uid="{ADAB04E6-A735-47D8-837B-578A113B2493}" name="檔案"/>
+    <tableColumn id="2" xr3:uid="{D3F91ED5-1226-438F-A188-D27B80D7C4E7}" name="原因"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10360,29 +10333,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39557176-3840-4E1D-A1DC-4632C2405308}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15405D6F-41B9-4037-A093-0C57789F5121}">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21.5" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -10398,11 +10370,8 @@
       <c r="E4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -10416,9 +10385,6 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -10437,30 +10403,29 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DBDB70-5572-4EF9-A6D7-E091B496893C}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA470CB-3F0D-4839-B6B0-A48D52B92490}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
@@ -10469,16 +10434,13 @@
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
         <v>49</v>
       </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>43</v>
       </c>
@@ -10497,13 +10459,10 @@
       <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -10518,9 +10477,6 @@
         <v>0</v>
       </c>
       <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -10531,48 +10487,44 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B1CF52-BA00-49BE-A1A5-6ACF8EF6B355}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E69E414-6E1C-44FD-8864-17AD0406113A}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
         <v>49</v>
       </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>43</v>
       </c>
@@ -10591,13 +10543,10 @@
       <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -10612,9 +10561,6 @@
         <v>0</v>
       </c>
       <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -10625,22 +10571,22 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CEE2C0-69FA-4ABA-9E33-33E2A318D707}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BB783D-AD97-49CC-AB3E-57243D0E3D91}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -10656,7 +10602,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -10669,7 +10615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD900A9-5DA0-4092-92F8-A1CDCAD84FB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AD313F-9B41-4601-A883-2533F6A41B07}">
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
@@ -10972,7 +10918,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF88AADA-2DC3-4965-92F6-06BB5297C9BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1945BE6-8D2A-44CF-8A68-BD52550E8025}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
@@ -10981,18 +10927,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -11005,18 +10951,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F87E89-B9D6-496B-833D-C4E6D93FCFEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E9ABA6-64AA-48D2-9A82-AF0394E2B244}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" ht="21.5" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -11034,18 +10980,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7911282-98EC-4747-A8C0-ED1C0EC2A384}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F305367-F9DB-44BB-ACC8-6A5005BC6A8D}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -11053,18 +10999,18 @@
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -11080,7 +11026,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -11096,18 +11042,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184EBCD5-6D98-4673-9274-0916EEDF1A04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82802975-9AC7-4CB3-AC2A-59AB1667A2FA}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -11115,18 +11061,18 @@
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4">
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -11142,7 +11088,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -11158,30 +11104,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86EBA47-545B-459D-9CEC-4DDF1339D2AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF9CA93-B243-4597-AD43-7C5C6141D5A1}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
         <v>47</v>
@@ -11203,7 +11149,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -11222,18 +11168,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601CF029-841A-4281-A37A-DC79821D26E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C099AB-4CDA-4258-B0A1-0658DC495F61}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -11241,18 +11187,18 @@
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -11279,7 +11225,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -11295,18 +11241,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3F26B5-E571-48A5-98D0-6FA8C2E9C782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD4E396-51FC-4715-A93B-2594F6C9B990}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -11314,18 +11260,18 @@
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -11341,7 +11287,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -11357,18 +11303,18 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7A977D-83BB-402A-91E4-D23BB940CE9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814E1678-E537-4BC9-845E-1FD1B554C445}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -11376,18 +11322,18 @@
         <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -11403,7 +11349,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -11419,35 +11365,35 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6ECF98-E59A-4847-852F-4E406C5B81F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443E9EF1-897F-44EC-8319-B373F4839F31}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
         <v>63</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>65</v>
-      </c>
-      <c r="E3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -11469,7 +11415,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
